--- a/test_checked.xlsx
+++ b/test_checked.xlsx
@@ -1662,6 +1662,11 @@
       <c r="F1" s="15" t="n"/>
       <c r="G1" s="15" t="n"/>
       <c r="H1" s="15" t="n"/>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>处理方案</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="150" customHeight="1" s="9">
       <c r="A2" s="41" t="inlineStr">
@@ -2261,6 +2266,11 @@
       </c>
       <c r="R13" s="65" t="inlineStr">
         <is>
+          <t>电信/联通</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>与第12行重复</t>
         </is>
       </c>
@@ -2404,6 +2414,11 @@
           <t>电信/联通</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>与第15,101行重复</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="9">
       <c r="A17" s="56" t="n">
@@ -2624,7 +2639,7 @@
       <c r="Q21" s="80" t="n">
         <v>45868</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>与第20行重复</t>
         </is>
@@ -4893,7 +4908,11 @@
         <v>45884</v>
       </c>
       <c r="R64" s="77" t="n"/>
-      <c r="S64" s="77" t="n"/>
+      <c r="S64" s="77" t="inlineStr">
+        <is>
+          <t>与第36,109行重复</t>
+        </is>
+      </c>
       <c r="T64" s="77" t="n"/>
       <c r="U64" s="77" t="n"/>
       <c r="V64" s="77" t="n"/>
@@ -5341,7 +5360,11 @@
         <v>45884</v>
       </c>
       <c r="R72" s="77" t="n"/>
-      <c r="S72" s="77" t="n"/>
+      <c r="S72" s="77" t="inlineStr">
+        <is>
+          <t>与第4,102行重复</t>
+        </is>
+      </c>
       <c r="T72" s="77" t="n"/>
       <c r="U72" s="77" t="n"/>
       <c r="V72" s="77" t="n"/>
@@ -6381,12 +6404,12 @@
       <c r="Q91" s="80" t="n">
         <v>45884</v>
       </c>
-      <c r="R91" s="77" t="inlineStr">
+      <c r="R91" s="77" t="n"/>
+      <c r="S91" s="77" t="inlineStr">
         <is>
           <t>与第29行重复</t>
         </is>
       </c>
-      <c r="S91" s="77" t="n"/>
       <c r="T91" s="77" t="n"/>
       <c r="U91" s="77" t="n"/>
       <c r="V91" s="77" t="n"/>
@@ -6938,12 +6961,12 @@
       <c r="Q101" s="80" t="n">
         <v>45884</v>
       </c>
-      <c r="R101" s="77" t="inlineStr">
+      <c r="R101" s="77" t="n"/>
+      <c r="S101" s="77" t="inlineStr">
         <is>
           <t>与第15,16行重复</t>
         </is>
       </c>
-      <c r="S101" s="77" t="n"/>
       <c r="T101" s="77" t="n"/>
       <c r="U101" s="77" t="n"/>
       <c r="V101" s="77" t="n"/>
@@ -6998,12 +7021,12 @@
       <c r="Q102" s="80" t="n">
         <v>45884</v>
       </c>
-      <c r="R102" s="77" t="inlineStr">
+      <c r="R102" s="77" t="n"/>
+      <c r="S102" s="77" t="inlineStr">
         <is>
           <t>与第4,72行重复</t>
         </is>
       </c>
-      <c r="S102" s="77" t="n"/>
       <c r="T102" s="77" t="n"/>
       <c r="U102" s="77" t="n"/>
       <c r="V102" s="77" t="n"/>
@@ -7160,12 +7183,12 @@
       <c r="Q105" s="80" t="n">
         <v>45884</v>
       </c>
-      <c r="R105" s="77" t="inlineStr">
+      <c r="R105" s="77" t="n"/>
+      <c r="S105" s="77" t="inlineStr">
         <is>
           <t>与第25行重复</t>
         </is>
       </c>
-      <c r="S105" s="77" t="n"/>
       <c r="T105" s="77" t="n"/>
       <c r="U105" s="77" t="n"/>
       <c r="V105" s="77" t="n"/>
@@ -7388,12 +7411,12 @@
       <c r="Q109" s="80" t="n">
         <v>45884</v>
       </c>
-      <c r="R109" s="77" t="inlineStr">
+      <c r="R109" s="77" t="n"/>
+      <c r="S109" s="77" t="inlineStr">
         <is>
           <t>与第36,64行重复</t>
         </is>
       </c>
-      <c r="S109" s="77" t="n"/>
       <c r="T109" s="77" t="n"/>
       <c r="U109" s="77" t="n"/>
       <c r="V109" s="77" t="n"/>
@@ -10474,10 +10497,14 @@
       </c>
       <c r="R164" s="77" t="inlineStr">
         <is>
+          <t>20250819161739X459466593</t>
+        </is>
+      </c>
+      <c r="S164" s="77" t="inlineStr">
+        <is>
           <t>与第31行重复</t>
         </is>
       </c>
-      <c r="S164" s="77" t="n"/>
       <c r="T164" s="77" t="n"/>
       <c r="U164" s="77" t="n"/>
       <c r="V164" s="77" t="n"/>

--- a/test_checked.xlsx
+++ b/test_checked.xlsx
@@ -2269,11 +2269,6 @@
           <t>电信/联通</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>与第12行重复</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="9">
       <c r="A14" s="56" t="n">
@@ -2318,6 +2313,11 @@
         <v>45868</v>
       </c>
       <c r="R14" s="65" t="n"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>与第13行重复</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="9">
       <c r="A15" s="56" t="n">
@@ -2414,11 +2414,6 @@
           <t>电信/联通</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>与第15,101行重复</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="9">
       <c r="A17" s="56" t="n">
@@ -2467,6 +2462,11 @@
           <t>电信/联通</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>与第16,102行重复</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15.6" customHeight="1" s="9">
       <c r="A18" s="56" t="n">
@@ -2639,11 +2639,6 @@
       <c r="Q21" s="80" t="n">
         <v>45868</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>与第20行重复</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="56" t="n">
@@ -2686,6 +2681,11 @@
       <c r="P22" s="42" t="n"/>
       <c r="Q22" s="80" t="n">
         <v>45868</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>与第21行重复</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -4908,11 +4908,7 @@
         <v>45884</v>
       </c>
       <c r="R64" s="77" t="n"/>
-      <c r="S64" s="77" t="inlineStr">
-        <is>
-          <t>与第36,109行重复</t>
-        </is>
-      </c>
+      <c r="S64" s="77" t="n"/>
       <c r="T64" s="77" t="n"/>
       <c r="U64" s="77" t="n"/>
       <c r="V64" s="77" t="n"/>
@@ -4968,7 +4964,11 @@
         <v>45884</v>
       </c>
       <c r="R65" s="59" t="n"/>
-      <c r="S65" s="59" t="n"/>
+      <c r="S65" s="59" t="inlineStr">
+        <is>
+          <t>与第37,110行重复</t>
+        </is>
+      </c>
       <c r="T65" s="59" t="n"/>
       <c r="U65" s="59" t="n"/>
       <c r="V65" s="59" t="n"/>
@@ -5360,11 +5360,7 @@
         <v>45884</v>
       </c>
       <c r="R72" s="77" t="n"/>
-      <c r="S72" s="77" t="inlineStr">
-        <is>
-          <t>与第4,102行重复</t>
-        </is>
-      </c>
+      <c r="S72" s="77" t="n"/>
       <c r="T72" s="77" t="n"/>
       <c r="U72" s="77" t="n"/>
       <c r="V72" s="77" t="n"/>
@@ -5420,6 +5416,11 @@
       <c r="R73" s="35" t="inlineStr">
         <is>
           <t>电信/联通</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>与第5,103行重复</t>
         </is>
       </c>
     </row>
@@ -6405,11 +6406,7 @@
         <v>45884</v>
       </c>
       <c r="R91" s="77" t="n"/>
-      <c r="S91" s="77" t="inlineStr">
-        <is>
-          <t>与第29行重复</t>
-        </is>
-      </c>
+      <c r="S91" s="77" t="n"/>
       <c r="T91" s="77" t="n"/>
       <c r="U91" s="77" t="n"/>
       <c r="V91" s="77" t="n"/>
@@ -6468,6 +6465,11 @@
         <is>
           <t>36.133.125.149/32
 36.133.125.229/32</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>与第30行重复</t>
         </is>
       </c>
     </row>
@@ -6962,11 +6964,7 @@
         <v>45884</v>
       </c>
       <c r="R101" s="77" t="n"/>
-      <c r="S101" s="77" t="inlineStr">
-        <is>
-          <t>与第15,16行重复</t>
-        </is>
-      </c>
+      <c r="S101" s="77" t="n"/>
       <c r="T101" s="77" t="n"/>
       <c r="U101" s="77" t="n"/>
       <c r="V101" s="77" t="n"/>
@@ -7024,7 +7022,7 @@
       <c r="R102" s="77" t="n"/>
       <c r="S102" s="77" t="inlineStr">
         <is>
-          <t>与第4,72行重复</t>
+          <t>与第16,17行重复</t>
         </is>
       </c>
       <c r="T102" s="77" t="n"/>
@@ -7082,6 +7080,11 @@
       <c r="R103" s="35" t="inlineStr">
         <is>
           <t>电信/联通</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>与第5,73行重复</t>
         </is>
       </c>
     </row>
@@ -7184,11 +7187,7 @@
         <v>45884</v>
       </c>
       <c r="R105" s="77" t="n"/>
-      <c r="S105" s="77" t="inlineStr">
-        <is>
-          <t>与第25行重复</t>
-        </is>
-      </c>
+      <c r="S105" s="77" t="n"/>
       <c r="T105" s="77" t="n"/>
       <c r="U105" s="77" t="n"/>
       <c r="V105" s="77" t="n"/>
@@ -7244,7 +7243,11 @@
         <v>45884</v>
       </c>
       <c r="R106" s="77" t="n"/>
-      <c r="S106" s="77" t="n"/>
+      <c r="S106" s="77" t="inlineStr">
+        <is>
+          <t>与第26行重复</t>
+        </is>
+      </c>
       <c r="T106" s="77" t="n"/>
       <c r="U106" s="77" t="n"/>
       <c r="V106" s="77" t="n"/>
@@ -7412,11 +7415,7 @@
         <v>45884</v>
       </c>
       <c r="R109" s="77" t="n"/>
-      <c r="S109" s="77" t="inlineStr">
-        <is>
-          <t>与第36,64行重复</t>
-        </is>
-      </c>
+      <c r="S109" s="77" t="n"/>
       <c r="T109" s="77" t="n"/>
       <c r="U109" s="77" t="n"/>
       <c r="V109" s="77" t="n"/>
@@ -7472,7 +7471,11 @@
         <v>45884</v>
       </c>
       <c r="R110" s="59" t="n"/>
-      <c r="S110" s="59" t="n"/>
+      <c r="S110" s="59" t="inlineStr">
+        <is>
+          <t>与第37,65行重复</t>
+        </is>
+      </c>
       <c r="T110" s="59" t="n"/>
       <c r="U110" s="59" t="n"/>
       <c r="V110" s="59" t="n"/>
@@ -10500,11 +10503,7 @@
           <t>20250819161739X459466593</t>
         </is>
       </c>
-      <c r="S164" s="77" t="inlineStr">
-        <is>
-          <t>与第31行重复</t>
-        </is>
-      </c>
+      <c r="S164" s="77" t="n"/>
       <c r="T164" s="77" t="n"/>
       <c r="U164" s="77" t="n"/>
       <c r="V164" s="77" t="n"/>
@@ -10560,7 +10559,11 @@
         <v>45889</v>
       </c>
       <c r="R165" s="77" t="n"/>
-      <c r="S165" s="77" t="n"/>
+      <c r="S165" s="77" t="inlineStr">
+        <is>
+          <t>与第32行重复</t>
+        </is>
+      </c>
       <c r="T165" s="77" t="n"/>
       <c r="U165" s="77" t="n"/>
       <c r="V165" s="77" t="n"/>

--- a/test_checked.xlsx
+++ b/test_checked.xlsx
@@ -2325,7 +2325,7 @@
       </c>
       <c r="B15" s="43" t="inlineStr">
         <is>
-          <t>36.133.128.188</t>
+          <t>36.133.128.188/32</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B23" s="43" t="inlineStr">
         <is>
-          <t>36.139.124.119</t>
+          <t>36.139.124.119/32</t>
         </is>
       </c>
       <c r="C23" s="19" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="B24" s="43" t="inlineStr">
         <is>
-          <t>36.137.246.216</t>
+          <t>36.137.246.216/32</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B27" s="43" t="inlineStr">
         <is>
-          <t>36.134.44.69</t>
+          <t>36.134.44.69/32</t>
         </is>
       </c>
       <c r="C27" s="19" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B28" s="43" t="inlineStr">
         <is>
-          <t>36.140.115.235</t>
+          <t>36.140.115.235/32</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B29" s="43" t="inlineStr">
         <is>
-          <t>36.139.124.40</t>
+          <t>36.139.124.40/32</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B55" s="28" t="inlineStr">
         <is>
-          <t>36.134.41.45</t>
+          <t>36.134.41.45/32</t>
         </is>
       </c>
       <c r="C55" s="19" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>36.134.41.87</t>
+          <t>36.134.41.87/32</t>
         </is>
       </c>
       <c r="C77" s="19" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B113" s="43" t="inlineStr">
         <is>
-          <t>36.213.196.6</t>
+          <t>36.213.196.6/32</t>
         </is>
       </c>
       <c r="C113" s="19" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="B114" s="43" t="inlineStr">
         <is>
-          <t>36.213.196.71</t>
+          <t>36.213.196.71/32</t>
         </is>
       </c>
       <c r="C114" s="19" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="B115" s="43" t="inlineStr">
         <is>
-          <t>36.213.196.77</t>
+          <t>36.213.196.77/32</t>
         </is>
       </c>
       <c r="C115" s="19" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="B116" s="43" t="inlineStr">
         <is>
-          <t>36.213.196.9</t>
+          <t>36.213.196.9/32</t>
         </is>
       </c>
       <c r="C116" s="19" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="B117" s="43" t="inlineStr">
         <is>
-          <t>36.213.197.150</t>
+          <t>36.213.197.150/32</t>
         </is>
       </c>
       <c r="C117" s="19" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="B118" s="43" t="inlineStr">
         <is>
-          <t>36.213.197.199</t>
+          <t>36.213.197.199/32</t>
         </is>
       </c>
       <c r="C118" s="19" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="B119" s="43" t="inlineStr">
         <is>
-          <t>36.213.197.203</t>
+          <t>36.213.197.203/32</t>
         </is>
       </c>
       <c r="C119" s="19" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="B120" s="43" t="inlineStr">
         <is>
-          <t>36.213.197.224</t>
+          <t>36.213.197.224/32</t>
         </is>
       </c>
       <c r="C120" s="19" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="B121" s="43" t="inlineStr">
         <is>
-          <t>36.213.197.38</t>
+          <t>36.213.197.38/32</t>
         </is>
       </c>
       <c r="C121" s="19" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="B122" s="43" t="inlineStr">
         <is>
-          <t>36.213.199.156</t>
+          <t>36.213.199.156/32</t>
         </is>
       </c>
       <c r="C122" s="19" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="B123" s="43" t="inlineStr">
         <is>
-          <t>36.213.199.175</t>
+          <t>36.213.199.175/32</t>
         </is>
       </c>
       <c r="C123" s="19" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="B124" s="43" t="inlineStr">
         <is>
-          <t>36.213.199.231</t>
+          <t>36.213.199.231/32</t>
         </is>
       </c>
       <c r="C124" s="19" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="B125" s="43" t="inlineStr">
         <is>
-          <t>36.213.199.237</t>
+          <t>36.213.199.237/32</t>
         </is>
       </c>
       <c r="C125" s="19" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="B126" s="43" t="inlineStr">
         <is>
-          <t>36.213.199.30</t>
+          <t>36.213.199.30/32</t>
         </is>
       </c>
       <c r="C126" s="19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="B127" s="43" t="inlineStr">
         <is>
-          <t>36.213.199.51</t>
+          <t>36.213.199.51/32</t>
         </is>
       </c>
       <c r="C127" s="19" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="B128" s="43" t="inlineStr">
         <is>
-          <t>36.213.200.135</t>
+          <t>36.213.200.135/32</t>
         </is>
       </c>
       <c r="C128" s="19" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="B129" s="43" t="inlineStr">
         <is>
-          <t>36.213.202.20</t>
+          <t>36.213.202.20/32</t>
         </is>
       </c>
       <c r="C129" s="19" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="B130" s="43" t="inlineStr">
         <is>
-          <t>36.213.202.29</t>
+          <t>36.213.202.29/32</t>
         </is>
       </c>
       <c r="C130" s="19" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="B131" s="43" t="inlineStr">
         <is>
-          <t>36.213.202.3</t>
+          <t>36.213.202.3/32</t>
         </is>
       </c>
       <c r="C131" s="19" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="B132" s="43" t="inlineStr">
         <is>
-          <t>36.213.202.54</t>
+          <t>36.213.202.54/32</t>
         </is>
       </c>
       <c r="C132" s="19" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="B133" s="43" t="inlineStr">
         <is>
-          <t>36.213.206.107</t>
+          <t>36.213.206.107/32</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="B134" s="43" t="inlineStr">
         <is>
-          <t>36.213.206.108</t>
+          <t>36.213.206.108/32</t>
         </is>
       </c>
       <c r="C134" s="19" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="B135" s="43" t="inlineStr">
         <is>
-          <t>36.213.206.123</t>
+          <t>36.213.206.123/32</t>
         </is>
       </c>
       <c r="C135" s="19" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="B136" s="43" t="inlineStr">
         <is>
-          <t>36.213.206.15</t>
+          <t>36.213.206.15/32</t>
         </is>
       </c>
       <c r="C136" s="19" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="B137" s="43" t="inlineStr">
         <is>
-          <t>36.213.206.158</t>
+          <t>36.213.206.158/32</t>
         </is>
       </c>
       <c r="C137" s="19" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="B138" s="43" t="inlineStr">
         <is>
-          <t>36.213.206.18</t>
+          <t>36.213.206.18/32</t>
         </is>
       </c>
       <c r="C138" s="19" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="B139" s="43" t="inlineStr">
         <is>
-          <t>36.213.206.211</t>
+          <t>36.213.206.211/32</t>
         </is>
       </c>
       <c r="C139" s="19" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="B140" s="43" t="inlineStr">
         <is>
-          <t>36.213.206.228</t>
+          <t>36.213.206.228/32</t>
         </is>
       </c>
       <c r="C140" s="19" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="B141" s="43" t="inlineStr">
         <is>
-          <t>36.213.206.233</t>
+          <t>36.213.206.233/32</t>
         </is>
       </c>
       <c r="C141" s="19" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="B142" s="43" t="inlineStr">
         <is>
-          <t>36.213.207.197</t>
+          <t>36.213.207.197/32</t>
         </is>
       </c>
       <c r="C142" s="19" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="B143" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.123</t>
+          <t>36.213.208.123/32</t>
         </is>
       </c>
       <c r="C143" s="19" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="B144" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.184</t>
+          <t>36.213.208.184/32</t>
         </is>
       </c>
       <c r="C144" s="19" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="B145" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.199</t>
+          <t>36.213.208.199/32</t>
         </is>
       </c>
       <c r="C145" s="19" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="B146" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.204</t>
+          <t>36.213.208.204/32</t>
         </is>
       </c>
       <c r="C146" s="19" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="B147" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.210</t>
+          <t>36.213.208.210/32</t>
         </is>
       </c>
       <c r="C147" s="19" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="B148" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.220</t>
+          <t>36.213.208.220/32</t>
         </is>
       </c>
       <c r="C148" s="19" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="B149" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.221</t>
+          <t>36.213.208.221/32</t>
         </is>
       </c>
       <c r="C149" s="19" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="B150" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.226</t>
+          <t>36.213.208.226/32</t>
         </is>
       </c>
       <c r="C150" s="19" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="B151" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.33</t>
+          <t>36.213.208.33/32</t>
         </is>
       </c>
       <c r="C151" s="19" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="B152" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.61</t>
+          <t>36.213.208.61/32</t>
         </is>
       </c>
       <c r="C152" s="19" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="B153" s="43" t="inlineStr">
         <is>
-          <t>36.213.208.9</t>
+          <t>36.213.208.9/32</t>
         </is>
       </c>
       <c r="C153" s="19" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="B154" s="43" t="inlineStr">
         <is>
-          <t>36.213.209.104</t>
+          <t>36.213.209.104/32</t>
         </is>
       </c>
       <c r="C154" s="19" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="B155" s="43" t="inlineStr">
         <is>
-          <t>36.213.209.127</t>
+          <t>36.213.209.127/32</t>
         </is>
       </c>
       <c r="C155" s="19" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B156" s="43" t="inlineStr">
         <is>
-          <t>36.213.209.132</t>
+          <t>36.213.209.132/32</t>
         </is>
       </c>
       <c r="C156" s="19" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="B157" s="43" t="inlineStr">
         <is>
-          <t>36.213.209.133</t>
+          <t>36.213.209.133/32</t>
         </is>
       </c>
       <c r="C157" s="19" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="B158" s="43" t="inlineStr">
         <is>
-          <t>36.213.209.182</t>
+          <t>36.213.209.182/32</t>
         </is>
       </c>
       <c r="C158" s="19" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="B159" s="43" t="inlineStr">
         <is>
-          <t>36.213.209.21</t>
+          <t>36.213.209.21/32</t>
         </is>
       </c>
       <c r="C159" s="19" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="B160" s="43" t="inlineStr">
         <is>
-          <t>36.213.209.244</t>
+          <t>36.213.209.244/32</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="B161" s="43" t="inlineStr">
         <is>
-          <t>36.213.209.29</t>
+          <t>36.213.209.29/32</t>
         </is>
       </c>
       <c r="C161" s="19" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="B162" s="43" t="inlineStr">
         <is>
-          <t>36.213.209.74</t>
+          <t>36.213.209.74/32</t>
         </is>
       </c>
       <c r="C162" s="19" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="B163" s="43" t="inlineStr">
         <is>
-          <t>36.213.209.92</t>
+          <t>36.213.209.92/32</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
